--- a/data/trans_orig/P0802-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2007</t>
+          <t>Población según limitación a subir varios pisos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>217750</t>
+          <t>218654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>240689</t>
+          <t>241433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>197677</t>
+          <t>198096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223269</t>
+          <t>223941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>423514</t>
+          <t>421513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>458511</t>
+          <t>459371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42786</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30401</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54508</t>
+          <t>54620</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58472</t>
+          <t>58528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90546</t>
+          <t>91196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408425</t>
+          <t>407878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440549</t>
+          <t>439133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360410</t>
+          <t>359708</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>398509</t>
+          <t>397220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>782154</t>
+          <t>781174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>833000</t>
+          <t>830639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64919</t>
+          <t>65382</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61952</t>
+          <t>63583</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95053</t>
+          <t>95914</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107716</t>
+          <t>109416</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>150351</t>
+          <t>153272</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59020</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>46809</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78169</t>
+          <t>80027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>269610</t>
+          <t>269726</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>292323</t>
+          <t>292229</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>234517</t>
+          <t>234940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>265284</t>
+          <t>265296</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>510139</t>
+          <t>512272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>549620</t>
+          <t>551475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42219</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52666</t>
+          <t>51632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79834</t>
+          <t>80282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79152</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115400</t>
+          <t>113559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>36977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>299260</t>
+          <t>300541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>324747</t>
+          <t>324337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267866</t>
+          <t>268709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298981</t>
+          <t>300498</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>574363</t>
+          <t>577561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>617553</t>
+          <t>617985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26195</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48961</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56176</t>
+          <t>55733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86407</t>
+          <t>85264</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89067</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128597</t>
+          <t>126276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26195</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175310</t>
+          <t>174707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191373</t>
+          <t>190673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>156170</t>
+          <t>156670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>180109</t>
+          <t>178838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338436</t>
+          <t>337187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366129</t>
+          <t>366138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>17012</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>50493</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>215392</t>
+          <t>215911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>239652</t>
+          <t>239780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>190765</t>
+          <t>192536</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>220536</t>
+          <t>221593</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>415745</t>
+          <t>417030</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>452595</t>
+          <t>453046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26123</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48399</t>
+          <t>48552</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42994</t>
+          <t>42121</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68931</t>
+          <t>67991</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>75381</t>
+          <t>75940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110340</t>
+          <t>109563</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>32398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>501702</t>
+          <t>502294</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>535570</t>
+          <t>536207</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>470104</t>
+          <t>467534</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>511001</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>981372</t>
+          <t>984351</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1037420</t>
+          <t>1037258</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>88912</t>
+          <t>88614</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84149</t>
+          <t>85480</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121711</t>
+          <t>121577</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>154082</t>
+          <t>150144</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>200503</t>
+          <t>201042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>34732</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58436</t>
+          <t>57875</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>52719</t>
+          <t>52223</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>84879</t>
+          <t>84168</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>615121</t>
+          <t>616972</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>652724</t>
+          <t>653896</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>576241</t>
+          <t>572612</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>623203</t>
+          <t>621783</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1204100</t>
+          <t>1201979</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1263016</t>
+          <t>1266099</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>53455</t>
+          <t>52496</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>85036</t>
+          <t>83686</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>114011</t>
+          <t>114320</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>156233</t>
+          <t>158367</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>175715</t>
+          <t>174113</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>229119</t>
+          <t>227644</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30321</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>53994</t>
+          <t>55120</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>36388</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>65707</t>
+          <t>66232</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>74813</t>
+          <t>71991</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>112688</t>
+          <t>108522</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2781204</t>
+          <t>2780770</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2855843</t>
+          <t>2860304</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2540493</t>
+          <t>2542685</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2643450</t>
+          <t>2641918</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5345698</t>
+          <t>5353005</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5477417</t>
+          <t>5475675</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>301996</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>372599</t>
+          <t>371394</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>528502</t>
+          <t>532418</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>619138</t>
+          <t>623494</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>851342</t>
+          <t>852849</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>963313</t>
+          <t>960674</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>102165</t>
+          <t>101039</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>143626</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>186830</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>243588</t>
+          <t>243533</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>298915</t>
+          <t>301104</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>372125</t>
+          <t>371522</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2012</t>
+          <t>Población según limitación a subir varios pisos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>232982</t>
+          <t>234651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259097</t>
+          <t>259784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195366</t>
+          <t>194315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225416</t>
+          <t>224984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>437560</t>
+          <t>438479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>476426</t>
+          <t>477249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42820</t>
+          <t>41676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>26617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50067</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53583</t>
+          <t>54368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84460</t>
+          <t>86048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51045</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42580</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70944</t>
+          <t>70382</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409687</t>
+          <t>410692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445649</t>
+          <t>445264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368720</t>
+          <t>368289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409116</t>
+          <t>410547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>790999</t>
+          <t>792098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>849978</t>
+          <t>846451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>53600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58713</t>
+          <t>58773</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91699</t>
+          <t>94524</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93527</t>
+          <t>92137</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135752</t>
+          <t>133959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>45355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>75174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78249</t>
+          <t>79087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115879</t>
+          <t>120419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>256871</t>
+          <t>255859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285530</t>
+          <t>284799</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>244985</t>
+          <t>244234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>276923</t>
+          <t>277591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>513522</t>
+          <t>511949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>554721</t>
+          <t>553246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46960</t>
+          <t>46943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42386</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71222</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72262</t>
+          <t>71271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107017</t>
+          <t>107106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>29143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>31932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56869</t>
+          <t>57530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>297287</t>
+          <t>299766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328299</t>
+          <t>329163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>248378</t>
+          <t>247545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286163</t>
+          <t>285370</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>556221</t>
+          <t>559439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>603646</t>
+          <t>607483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>43735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41478</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67995</t>
+          <t>67820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69293</t>
+          <t>70865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105153</t>
+          <t>106384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39728</t>
+          <t>38252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53463</t>
+          <t>54417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76854</t>
+          <t>76514</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112162</t>
+          <t>114840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163251</t>
+          <t>162548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185812</t>
+          <t>186412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137913</t>
+          <t>136558</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165973</t>
+          <t>166046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308064</t>
+          <t>309264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>345753</t>
+          <t>344917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18111</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>39207</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31224</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55139</t>
+          <t>56372</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>55263</t>
+          <t>54233</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>89208</t>
+          <t>86302</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35809</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>48300</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>205675</t>
+          <t>205019</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>231576</t>
+          <t>230681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185797</t>
+          <t>182688</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>215965</t>
+          <t>213375</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>397888</t>
+          <t>398687</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>437985</t>
+          <t>437605</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26528</t>
+          <t>26207</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>48582</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43570</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69732</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77145</t>
+          <t>74998</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110769</t>
+          <t>110027</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>33072</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>55336</t>
+          <t>54676</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>554761</t>
+          <t>556350</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>591531</t>
+          <t>592777</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>493984</t>
+          <t>496605</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>542334</t>
+          <t>541517</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1061662</t>
+          <t>1064584</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1121998</t>
+          <t>1125057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>48457</t>
+          <t>48912</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80297</t>
+          <t>79077</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>99577</t>
+          <t>100095</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>141087</t>
+          <t>140590</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>158408</t>
+          <t>157375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>211258</t>
+          <t>209550</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33406</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>41319</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>72367</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60452</t>
+          <t>58234</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98581</t>
+          <t>96295</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>629526</t>
+          <t>629238</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>674084</t>
+          <t>674017</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>617453</t>
+          <t>618221</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>665481</t>
+          <t>666518</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1260220</t>
+          <t>1260568</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1325669</t>
+          <t>1325010</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>81262</t>
+          <t>81566</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>122244</t>
+          <t>122982</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>107831</t>
+          <t>107561</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>147995</t>
+          <t>148659</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>197598</t>
+          <t>198382</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>257621</t>
+          <t>258623</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36278</t>
+          <t>36858</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42324</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>69342</t>
+          <t>69847</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>61462</t>
+          <t>64093</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>99463</t>
+          <t>98145</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2843764</t>
+          <t>2847280</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2930525</t>
+          <t>2935148</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2587845</t>
+          <t>2588235</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2699763</t>
+          <t>2693905</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5468649</t>
+          <t>5464932</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5601630</t>
+          <t>5599342</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>327119</t>
+          <t>321248</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>397194</t>
+          <t>396264</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>524396</t>
+          <t>529916</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>612693</t>
+          <t>615914</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>873280</t>
+          <t>873010</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>985866</t>
+          <t>986556</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>148422</t>
+          <t>147007</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>202521</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>312034</t>
+          <t>313393</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>380918</t>
+          <t>385717</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>474979</t>
+          <t>482134</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>570104</t>
+          <t>568634</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2016</t>
+          <t>Población según limitación a subir varios pisos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225820</t>
+          <t>227022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253152</t>
+          <t>253640</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195617</t>
+          <t>194095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226237</t>
+          <t>225271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>428511</t>
+          <t>429294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>471926</t>
+          <t>471840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44001</t>
+          <t>44498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>48030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80706</t>
+          <t>79940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>30617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>35803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60385</t>
+          <t>62599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>53275</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86602</t>
+          <t>87176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426972</t>
+          <t>428562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>456169</t>
+          <t>456871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388645</t>
+          <t>390492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430493</t>
+          <t>429069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>828359</t>
+          <t>827828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>878669</t>
+          <t>877451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52240</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53682</t>
+          <t>54264</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87646</t>
+          <t>86371</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>88695</t>
+          <t>87540</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>128671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>30114</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>31670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57797</t>
+          <t>57844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>49129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82180</t>
+          <t>83413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264640</t>
+          <t>266267</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>286911</t>
+          <t>287116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>255437</t>
+          <t>256051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>287620</t>
+          <t>286387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>528907</t>
+          <t>530664</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>566338</t>
+          <t>569326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>25278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45988</t>
+          <t>45312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32973</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60673</t>
+          <t>60060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64424</t>
+          <t>62759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98528</t>
+          <t>96202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>299986</t>
+          <t>297611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>326709</t>
+          <t>326783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>265064</t>
+          <t>265799</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>302651</t>
+          <t>302954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>572465</t>
+          <t>574898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>622418</t>
+          <t>623463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38808</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61560</t>
+          <t>62826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60176</t>
+          <t>59697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93483</t>
+          <t>93057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>39715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40199</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71506</t>
+          <t>73980</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65177</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104626</t>
+          <t>100729</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174592</t>
+          <t>173822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192999</t>
+          <t>192282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158037</t>
+          <t>157154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182463</t>
+          <t>181379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>337275</t>
+          <t>338564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369141</t>
+          <t>369078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>32852</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>30136</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53402</t>
+          <t>53026</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49929</t>
+          <t>50750</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>79801</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194778</t>
+          <t>194882</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221327</t>
+          <t>221136</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>175103</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>207254</t>
+          <t>204385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>375873</t>
+          <t>378149</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>419456</t>
+          <t>419937</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>37095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37138</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63687</t>
+          <t>63093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60114</t>
+          <t>60813</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93806</t>
+          <t>93614</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>23165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46780</t>
+          <t>46857</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46253</t>
+          <t>45762</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77374</t>
+          <t>77039</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>527504</t>
+          <t>528642</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>568769</t>
+          <t>568326</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>507701</t>
+          <t>506674</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>553359</t>
+          <t>553787</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1044725</t>
+          <t>1049920</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1109483</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62256</t>
+          <t>62700</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>98918</t>
+          <t>99073</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76936</t>
+          <t>74902</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>113756</t>
+          <t>113200</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>149914</t>
+          <t>146759</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>203194</t>
+          <t>198688</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>38338</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49113</t>
+          <t>50865</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>84676</t>
+          <t>83368</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>74526</t>
+          <t>76340</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114429</t>
+          <t>116844</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>663407</t>
+          <t>664599</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>699202</t>
+          <t>700048</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>639535</t>
+          <t>638152</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>687631</t>
+          <t>686219</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1315448</t>
+          <t>1320918</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1377902</t>
+          <t>1381396</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>61970</t>
+          <t>62910</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>94574</t>
+          <t>95333</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>96950</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>139739</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>165751</t>
+          <t>164074</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>223101</t>
+          <t>220294</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>31372</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>63600</t>
+          <t>60387</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>82952</t>
+          <t>80475</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2858151</t>
+          <t>2857004</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2942999</t>
+          <t>2944841</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2680789</t>
+          <t>2682849</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2784995</t>
+          <t>2784478</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5571243</t>
+          <t>5573243</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5711331</t>
+          <t>5708616</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>303229</t>
+          <t>303815</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>376772</t>
+          <t>375847</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>452231</t>
+          <t>452050</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>537256</t>
+          <t>542378</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>777451</t>
+          <t>777516</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>886340</t>
+          <t>884242</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>179169</t>
+          <t>179052</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>284283</t>
+          <t>279409</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>354970</t>
+          <t>355076</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>426191</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>515728</t>
+          <t>511439</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2023</t>
+          <t>Población según limitación a subir varios pisos en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>252895</t>
+          <t>252809</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>277413</t>
+          <t>277890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222585</t>
+          <t>222734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>242436</t>
+          <t>243162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>484032</t>
+          <t>483744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>514295</t>
+          <t>514668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28263</t>
+          <t>27730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54528</t>
+          <t>54001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70219</t>
+          <t>68716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99039</t>
+          <t>97886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>12189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>26426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401550</t>
+          <t>403179</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440843</t>
+          <t>442660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372303</t>
+          <t>371787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>404928</t>
+          <t>401966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>786329</t>
+          <t>784420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>834783</t>
+          <t>835778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61365</t>
+          <t>59951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98500</t>
+          <t>95611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70840</t>
+          <t>70907</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96597</t>
+          <t>96838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139232</t>
+          <t>136883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>182255</t>
+          <t>184202</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28145</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33999</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55395</t>
+          <t>55122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>75697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>258811</t>
+          <t>258781</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>280363</t>
+          <t>280582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>270383</t>
+          <t>270080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>292047</t>
+          <t>292032</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>537625</t>
+          <t>536958</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>567081</t>
+          <t>566908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31306</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48807</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49330</t>
+          <t>48258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71675</t>
+          <t>72261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35193</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35349</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43073</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64550</t>
+          <t>64894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>239170</t>
+          <t>239097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268024</t>
+          <t>267833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371088</t>
+          <t>368674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>427929</t>
+          <t>426795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>622204</t>
+          <t>623102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>686787</t>
+          <t>687653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>42602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31135</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69923</t>
+          <t>71998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63751</t>
+          <t>61184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105407</t>
+          <t>104294</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16715</t>
+          <t>16716</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38352</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70076</t>
+          <t>69675</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149696</t>
+          <t>149375</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162789</t>
+          <t>162281</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185739</t>
+          <t>184557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228418</t>
+          <t>228644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342763</t>
+          <t>342797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384606</t>
+          <t>383019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56614</t>
+          <t>56839</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>40781</t>
+          <t>41226</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>73397</t>
+          <t>73495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>25819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>226997</t>
+          <t>226115</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>242696</t>
+          <t>242177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>197899</t>
+          <t>197037</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>215073</t>
+          <t>214804</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>430691</t>
+          <t>429252</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>453886</t>
+          <t>453393</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32337</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36321</t>
+          <t>36477</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54491</t>
+          <t>54634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21385</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31432</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>500380</t>
+          <t>500567</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>539538</t>
+          <t>539443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>629685</t>
+          <t>628269</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>766049</t>
+          <t>772026</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1155026</t>
+          <t>1154988</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1309519</t>
+          <t>1300666</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58733</t>
+          <t>58390</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92684</t>
+          <t>91642</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51328</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132321</t>
+          <t>135243</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>104412</t>
+          <t>111950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>209866</t>
+          <t>208698</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89556</t>
+          <t>90385</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>60769</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>115537</t>
+          <t>115372</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>263309</t>
+          <t>269126</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>814266</t>
+          <t>816298</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>524572</t>
+          <t>525259</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>564054</t>
+          <t>563998</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>707989</t>
+          <t>712050</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1349257</t>
+          <t>1350922</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>77514</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>651515</t>
+          <t>643465</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>93331</t>
+          <t>95174</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>128900</t>
+          <t>130130</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>196132</t>
+          <t>194007</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>881195</t>
+          <t>875593</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>40299</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>51740</t>
+          <t>51804</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>75168</t>
+          <t>74481</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>110627</t>
+          <t>111535</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2130097</t>
+          <t>2136835</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2946401</t>
+          <t>2946868</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2867523</t>
+          <t>2867724</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3084092</t>
+          <t>3085463</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4915696</t>
+          <t>5087714</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5898884</t>
+          <t>5904243</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>354394</t>
+          <t>353796</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1217135</t>
+          <t>1210510</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>410088</t>
+          <t>405299</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>547076</t>
+          <t>547031</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>840011</t>
+          <t>836345</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1870835</t>
+          <t>1789488</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>117959</t>
+          <t>118386</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>176816</t>
+          <t>177154</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>221814</t>
+          <t>226646</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>309173</t>
+          <t>308848</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>367088</t>
+          <t>371618</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>470483</t>
+          <t>472988</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
